--- a/docs/Me9_스토리보드_Ver3.0_필요파일_재정리_20260728.xlsx
+++ b/docs/Me9_스토리보드_Ver3.0_필요파일_재정리_20260728.xlsx
@@ -3,9 +3,10 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="신규_보강필요" sheetId="1" r:id="rId1"/>
-    <sheet name="구현확인" sheetId="2" r:id="rId2"/>
-    <sheet name="정산_메일요구" sheetId="3" r:id="rId3"/>
-    <sheet name="필요문서_결정사항" sheetId="4" r:id="rId4"/>
+    <sheet name="인덱스_임시화면" sheetId="2" r:id="rId2"/>
+    <sheet name="구현확인" sheetId="3" r:id="rId3"/>
+    <sheet name="정산_메일요구" sheetId="4" r:id="rId4"/>
+    <sheet name="필요문서_결정사항" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -47,12 +48,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="24" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
@@ -144,37 +145,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-04-02-1</t>
+          <t xml:space="preserve">RF-01-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">채널 관리자</t>
+          <t xml:space="preserve">홈페이지</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 채널 등록</t>
+          <t xml:space="preserve">main</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비공개 시 접속 가능 인원관리</t>
+          <t xml:space="preserve">메인 페이지</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Layer popup</t>
+          <t xml:space="preserve">Web Page</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">스토리보드 Ver3.0/작업요청서 기준. 공개여부가 비공개일 때 접속 허용 대상 관리 필요</t>
+          <t xml:space="preserve">스토리보드상 대표 이미지/회사 소개/이용방법/공지/회사정보가 있는 메인 화면</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -184,7 +185,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">보강필요</t>
+          <t xml:space="preserve">신규/재작업필요</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -194,39 +195,39 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 등록/수정 화면에는 공개/비공개 계열 설정은 있으나, 허용 회원 검색/추가/삭제 전용 관리 UI는 명확하지 않음</t>
+          <t xml:space="preserve">현재 resources/views/front/index.blade.php는 container 내부가 비어 있으며 “me9market/main/index.php 소스, container 내부는 비어 있었음” 주석만 존재</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel/shop_register.html 하위 Layer</t>
+          <t xml:space="preserve">/homepage/main/index.html</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel.sub01.shop_register / channel.sub01.info_update</t>
+          <t xml:space="preserve">/ route -&gt; front.index</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비공개 Shop 접속 가능 회원 관리 레이어 또는 동일 화면 내 관리 영역</t>
+          <t xml:space="preserve">홈페이지 메인 실제 퍼블리싱/콘텐츠/공지 추출/회사정보 영역 구현 필요</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">스토리보드상 독립 레이어 성격. 실제 운영에서는 회원 검색, 등록, 삭제, 목록 확인이 필요</t>
+          <t xml:space="preserve">파일 존재만으로 구현 완료로 볼 수 없음. 인덱스 누락 항목</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-04-02-5-2</t>
+          <t xml:space="preserve">RF-02-02-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -236,22 +237,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 채널 등록</t>
+          <t xml:space="preserve">대시보드</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">구매현황 문자알림 사용 화면</t>
+          <t xml:space="preserve">대시보드 구성화면</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Page/Layer</t>
+          <t xml:space="preserve">Web Page</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문/구매현황 문자알림 사용 여부와 과금 기준 UI 필요</t>
+          <t xml:space="preserve">채널관리자 첫 화면. 주문단계, 회원정보, 문의사항, 주문목록, 방문 채널 등 표시</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -261,7 +262,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">보강필요</t>
+          <t xml:space="preserve">구현확인/추가검수</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -271,64 +272,64 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SMS 모델/수수료 계산은 있으나 채널 등록/수정에서 알림 대상 상태별 설정 UI가 명확하지 않음</t>
+          <t xml:space="preserve">channel/index.blade.php는 실제 counts/recentOrders/recentInquiries를 사용하나 스토리보드의 바로가기 메뉴/서브관리 채널목록 등 일부 항목은 최종 검수 필요</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel/shop_register.html 하위 화면</t>
+          <t xml:space="preserve">channel/dashboard.html</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel.sub01.shop_register / channel.sub01.info_update</t>
+          <t xml:space="preserve">/channel -&gt; channel.index</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SMS 알림 사용여부, 대상 상태, 수수료 안내/저장 항목 보강</t>
+          <t xml:space="preserve">운영 데이터 연동은 있음. 스토리보드 구성요소 빠짐 여부 추가 검수</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ver3.0 정산에서도 SMS 수수료가 정산/청구 금액에 반영됨</t>
+          <t xml:space="preserve">인덱스성 화면이므로 별도 추적 필요</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-05-01-3</t>
+          <t xml:space="preserve">RF-05-02-01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">채널 관리자</t>
+          <t xml:space="preserve">전체관리자</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">상품 관리</t>
+          <t xml:space="preserve">대시보드</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">자사 상품 목록 &gt; 판매중지 예고신청</t>
+          <t xml:space="preserve">전체관리자 대시보드 구성화면</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Layer</t>
+          <t xml:space="preserve">Web Page</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FileMap 기준 Layer 필요</t>
+          <t xml:space="preserve">전체관리자 첫 화면. 블록 조합형 대시보드, 주문상태, 매출 Top20, 카테고리 Top20, 현황 리스트</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -338,7 +339,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">보강필요</t>
+          <t xml:space="preserve">재작업필요</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -348,64 +349,64 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 base product stop-notice route는 있으나 FileMap 명칭의 판매중지 예고신청 Layer와 1:1 화면 매칭은 부족</t>
+          <t xml:space="preserve">admin/dashboard.blade.php는 16/5/1/0/5/2/3, 0000-00-00, Red/Blue 차트 등 하드코딩 샘플이 남아 있음. AdminController가 넘기는 counts도 화면에서 사용하지 않음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel/pop.product_own_stop_request.html</t>
+          <t xml:space="preserve">FileMap Page Path 공란 / master main 참조</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel.product_base.stop_notice / product_own</t>
+          <t xml:space="preserve">/admin/dashboard -&gt; admin.dashboard</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">판매중지 예고신청 레이어 UI 및 목록 액션 연결 확인/보강</t>
+          <t xml:space="preserve">실제 주문/매출/카테고리/회원/신고/포인트 데이터 연동 대시보드로 재작업</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">스토리보드상 상품 목록의 하위 레이어</t>
+          <t xml:space="preserve">이전 산출물에서 가장 크게 누락된 인덱스 항목</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-05-01-4</t>
+          <t xml:space="preserve">RF-05-02-01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">채널 관리자</t>
+          <t xml:space="preserve">전체관리자</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">상품 관리</t>
+          <t xml:space="preserve">대시보드</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">자사 상품 목록 &gt; 판매 요청 목록</t>
+          <t xml:space="preserve">master/index 샘플 화면</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Layer</t>
+          <t xml:space="preserve">Web Page</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FileMap 기준 Layer 필요</t>
+          <t xml:space="preserve">전체관리자 대시보드와 유사한 샘플 파일</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -415,7 +416,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">보강필요</t>
+          <t xml:space="preserve">정리필요</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -425,64 +426,64 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 판매 요청 목록 전용 레이어가 확인되지 않음</t>
+          <t xml:space="preserve">resources/views/master/index.blade.php는 Channel A/user01/Reporter X/Red Blue 등 샘플 데이터. 실제 MasterController@index는 admin.dashboard로 redirect하므로 운영 route에서 사용되지 않음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel/pop.product_own_sale_request.html</t>
+          <t xml:space="preserve">Physical File 참조: master/main</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel.sub02.product_own 계열</t>
+          <t xml:space="preserve">/master -&gt; admin.dashboard redirect</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">판매 요청 목록 레이어 또는 탭 영역 보강</t>
+          <t xml:space="preserve">운영 미사용 샘플이면 제거 또는 FileMap상 패턴 참고 파일로 명확히 분리</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FileMap에 실제 Layer 산출물로 명시</t>
+          <t xml:space="preserve">현재 파일만 보면 구현된 것처럼 오판 가능</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-05-01-5</t>
+          <t xml:space="preserve">RF-05-02-02~11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">채널 관리자</t>
+          <t xml:space="preserve">전체관리자</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">상품 관리</t>
+          <t xml:space="preserve">디자인 패턴</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">자사 상품 목록 &gt; 게시 채널</t>
+          <t xml:space="preserve">admin/sub*, master/sub* 패턴/샘플 화면</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Layer</t>
+          <t xml:space="preserve">Page/Layer/Popup</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FileMap 기준 Layer 필요</t>
+          <t xml:space="preserve">일반 리스트, 보기, 입력, 팝업, 레이어, 로딩 패턴</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -492,7 +493,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">보강필요</t>
+          <t xml:space="preserve">임시/패턴파일</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -502,64 +503,64 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">게시 채널 목록 전용 레이어가 확인되지 않음</t>
+          <t xml:space="preserve">admin/sub01, sub02, sub03, view, newpage, layer_large 및 master/sub01~03은 홍길동/111111/테스트 내용/내용노출 등 샘플 데이터가 다수 남아 있음</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel/pop.product_own_publication_channel.html</t>
+          <t xml:space="preserve">/admin/sub01, /admin/sub02, /admin/sub03, /admin/view, /admin/newpage, /admin/loading</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel.sub02.product_own 계열</t>
+          <t xml:space="preserve">admin.sub.* / master.sub* redirect</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">게시 채널 확인 레이어 보강</t>
+          <t xml:space="preserve">운영 CRUD 화면으로 오해하지 않도록 패턴 파일로 분리 표기. 실제 전체관리자 업무화면은 별도 구현 필요</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">상품이 어느 Shop 채널에 게시되었는지 운영자가 확인해야 함</t>
+          <t xml:space="preserve">스토리보드 디자인 패턴용이면 완료 기준이 다르고, 운영 메뉴에 노출되면 문제</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-05-02-6</t>
+          <t xml:space="preserve">RF-03-05-01~05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">채널 관리자</t>
+          <t xml:space="preserve">Shop 채널</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">상품 등록/수정</t>
+          <t xml:space="preserve">주문영역</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">발주 담당자 찾기</t>
+          <t xml:space="preserve">shop/sub 주문 샘플 파일</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Layer</t>
+          <t xml:space="preserve">Page</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">상품 등록 화면 하위 발주 담당자 검색/선택</t>
+          <t xml:space="preserve">Shop 주문확인/상세/취소/반품/교환 샘플 파일</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -569,7 +570,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">보강필요</t>
+          <t xml:space="preserve">운영미연결/재작업필요</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -579,64 +580,64 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">상품 등록/수정 화면은 있으나 전용 발주 담당자 찾기 Layer는 명확하지 않음</t>
+          <t xml:space="preserve">resources/views/shop/sub/*.blade.php는 상품명 111111 등 정적 샘플이고 현재 운영 route는 front/shop/*를 사용함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel/pop.product_own_update_order_manager.html</t>
+          <t xml:space="preserve">shop/order_confirm.html, order_details.html, cancel_details.html 등</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel.sub02.product_base_edit</t>
+          <t xml:space="preserve">운영 route 미연결 샘플</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">발주 담당자 검색/선택 레이어 또는 동등 UI 보강</t>
+          <t xml:space="preserve">운영 Shop 주문 화면은 front/shop 쪽으로 실제 데이터 연결 필요. shop/sub는 샘플/참고로 분리</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">발주사 연동을 위해 상품별 발주 담당자 지정 흐름 필요</t>
+          <t xml:space="preserve">샘플 파일 존재 때문에 완료로 판단하면 안 됨</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-06-02-5</t>
+          <t xml:space="preserve">RF-03-04-03~05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">채널 관리자</t>
+          <t xml:space="preserve">Shop 채널</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">공동구매 관리</t>
+          <t xml:space="preserve">상품영역</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">발주 담당자 찾기</t>
+          <t xml:space="preserve">front/cart, checkout, payment index</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Popup</t>
+          <t xml:space="preserve">Page</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">공동구매 등록 화면 하위 발주 담당자 검색/선택</t>
+          <t xml:space="preserve">기존 쇼핑몰 템플릿 계열 화면</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -646,7 +647,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">보강필요</t>
+          <t xml:space="preserve">중복/정리필요</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -656,64 +657,64 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">공동구매 등록/수정은 있으나 발주 담당자 찾기 전용 팝업은 명확하지 않음</t>
+          <t xml:space="preserve">front/cart/index, front/checkout/index, front/payment/index는 기존 일반 쇼핑몰 템플릿 성격이고 Shop 채널 운영 흐름은 front/shop/cart/order_form/order_complete와 분리됨</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FileMap Page Path 공란 / Popup</t>
+          <t xml:space="preserve">기획 FileMap 직접 경로 아님</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel.joint_purchase.create/edit</t>
+          <t xml:space="preserve">front.cart/payment/checkout legacy</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">공동구매용 발주 담당자 검색/선택 팝업 또는 동등 UI 보강</t>
+          <t xml:space="preserve">운영에 사용할 화면과 미사용 템플릿을 명확히 분리</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">공동구매 상품도 발주 담당자와 연결되어야 발주사 흐름이 자연스러움</t>
+          <t xml:space="preserve">중복 화면이 있으면 검수자가 실제 구현 파일을 혼동함</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-07-05-2</t>
+          <t xml:space="preserve">RF-01-07-10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">채널 관리자</t>
+          <t xml:space="preserve">홈페이지/마이페이지</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 관리</t>
+          <t xml:space="preserve">회원영역</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">반품 보류</t>
+          <t xml:space="preserve">front/mypage/sub01/modify 샘플성 파일</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Layer</t>
+          <t xml:space="preserve">Page</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">반품 주문 상세 하위 액션</t>
+          <t xml:space="preserve">마이페이지 회원정보 수정 과거/샘플 화면</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -723,7 +724,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">보강필요</t>
+          <t xml:space="preserve">중복/정리필요</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -733,39 +734,39 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">반품 팝업 UI는 있으나 보류 상태 전환 action/사유 입력 흐름은 별도 검증 필요</t>
+          <t xml:space="preserve">운영 route는 /mypage/profile -&gt; front.mypage.profile 사용. sub01/modify는 abcde1234/홍길동 등 정적 값이 남아 있음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel/pop.order_return_request_pending.html</t>
+          <t xml:space="preserve">/homepage/mypage/member_update.html</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel.sub04.inc.pop_order_return</t>
+          <t xml:space="preserve">mypage.profile이 운영 매칭</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">반품 보류 상태 변경, 사유 입력, 저장 action 보강/검증</t>
+          <t xml:space="preserve">sub01/modify는 미사용 샘플이면 정리, 운영이면 실제 데이터/action 연결 필요</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 상태 흐름상 단순 표시가 아니라 상태 전환이 필요</t>
+          <t xml:space="preserve">정보수정 버튼 # 문제와 연결됐던 유형</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-07-05-3</t>
+          <t xml:space="preserve">RF-02-04-02-1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -775,22 +776,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 관리</t>
+          <t xml:space="preserve">Shop 채널 등록</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">반품 송장 수정</t>
+          <t xml:space="preserve">비공개 시 접속 가능 인원관리</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Layer</t>
+          <t xml:space="preserve">Layer popup</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">반품 주문 상세 하위 액션</t>
+          <t xml:space="preserve">스토리보드 Ver3.0/작업요청서 기준. 공개여부가 비공개일 때 접속 허용 대상 관리 필요</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -810,39 +811,39 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">반품 송장 수정 UI/action의 1:1 매칭 검증 필요</t>
+          <t xml:space="preserve">현재 등록/수정 화면에는 공개/비공개 계열 설정은 있으나, 허용 회원 검색/추가/삭제 전용 관리 UI는 명확하지 않음</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel/pop.order_return_request_invoice.html</t>
+          <t xml:space="preserve">channel/shop_register.html 하위 Layer</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel.sub04.inc.pop_order_return</t>
+          <t xml:space="preserve">channel.sub01.shop_register / channel.sub01.info_update</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">반품 회수/재배송 송장 수정 action 보강/검증</t>
+          <t xml:space="preserve">비공개 Shop 접속 가능 회원 관리 레이어 또는 동일 화면 내 관리 영역</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">배송사/송장번호 수정 CRUD 필요</t>
+          <t xml:space="preserve">스토리보드상 독립 레이어 성격. 실제 운영에서는 회원 검색, 등록, 삭제, 목록 확인이 필요</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-07-06-2</t>
+          <t xml:space="preserve">RF-02-04-02-5-2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -852,22 +853,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 관리</t>
+          <t xml:space="preserve">Shop 채널 등록</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 회수 전 보류</t>
+          <t xml:space="preserve">구매현황 문자알림 사용 화면</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Layer</t>
+          <t xml:space="preserve">Page/Layer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 주문 상세 하위 액션</t>
+          <t xml:space="preserve">주문/구매현황 문자알림 사용 여부와 과금 기준 UI 필요</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -887,39 +888,39 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 보류 UI는 있으나 회수 전 상태 전환 action 검증 필요</t>
+          <t xml:space="preserve">SMS 모델/수수료 계산은 있으나 채널 등록/수정에서 알림 대상 상태별 설정 UI가 명확하지 않음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel/pop.order_exchange_request_hold_before.html</t>
+          <t xml:space="preserve">channel/shop_register.html 하위 화면</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel.sub04.inc.pop_order_exchange</t>
+          <t xml:space="preserve">channel.sub01.shop_register / channel.sub01.info_update</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 회수 전 보류 상태/사유 저장 보강</t>
+          <t xml:space="preserve">SMS 알림 사용여부, 대상 상태, 수수료 안내/저장 항목 보강</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 상태 전이가 여러 단계로 분리됨</t>
+          <t xml:space="preserve">Ver3.0 정산에서도 SMS 수수료가 정산/청구 금액에 반영됨</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-07-06-6</t>
+          <t xml:space="preserve">RF-02-05-01-3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -929,12 +930,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 관리</t>
+          <t xml:space="preserve">상품 관리</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 회수 후 보류</t>
+          <t xml:space="preserve">자사 상품 목록 &gt; 판매중지 예고신청</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -944,7 +945,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 주문 상세 하위 액션</t>
+          <t xml:space="preserve">FileMap 기준 Layer 필요</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -964,39 +965,39 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 회수 후 보류 상태 전환 action 검증 필요</t>
+          <t xml:space="preserve">현재 base product stop-notice route는 있으나 FileMap 명칭의 판매중지 예고신청 Layer와 1:1 화면 매칭은 부족</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel/pop.order_exchange_request_hold_after.html</t>
+          <t xml:space="preserve">channel/pop.product_own_stop_request.html</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel.sub04.inc.pop_order_exchange</t>
+          <t xml:space="preserve">channel.product_base.stop_notice / product_own</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 회수 후 보류 상태/사유 저장 보강</t>
+          <t xml:space="preserve">판매중지 예고신청 레이어 UI 및 목록 액션 연결 확인/보강</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">회수 전/후 보류가 스토리보드에서 분리됨</t>
+          <t xml:space="preserve">스토리보드상 상품 목록의 하위 레이어</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-07-06-8</t>
+          <t xml:space="preserve">RF-02-05-01-4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1006,12 +1007,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 관리</t>
+          <t xml:space="preserve">상품 관리</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 옵션 변경</t>
+          <t xml:space="preserve">자사 상품 목록 &gt; 판매 요청 목록</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1021,7 +1022,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 주문 상세 하위 액션</t>
+          <t xml:space="preserve">FileMap 기준 Layer 필요</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1041,39 +1042,39 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 옵션 변경 저장 action의 1:1 매칭 검증 필요</t>
+          <t xml:space="preserve">현재 판매 요청 목록 전용 레이어가 확인되지 않음</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel/pop.order_exchange_request_option.html</t>
+          <t xml:space="preserve">channel/pop.product_own_sale_request.html</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel.sub04.inc.pop_order_exchange</t>
+          <t xml:space="preserve">channel.sub02.product_own 계열</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 상품 옵션 변경 UI/action 보강</t>
+          <t xml:space="preserve">판매 요청 목록 레이어 또는 탭 영역 보강</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 대상 옵션 변경은 주문상품 데이터 수정과 연결됨</t>
+          <t xml:space="preserve">FileMap에 실제 Layer 산출물로 명시</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-07-06-9</t>
+          <t xml:space="preserve">RF-02-05-01-5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1083,12 +1084,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 관리</t>
+          <t xml:space="preserve">상품 관리</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 송장 수정</t>
+          <t xml:space="preserve">자사 상품 목록 &gt; 게시 채널</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1098,7 +1099,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 주문 상세 하위 액션</t>
+          <t xml:space="preserve">FileMap 기준 Layer 필요</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1118,39 +1119,39 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 송장 수정 UI/action의 1:1 매칭 검증 필요</t>
+          <t xml:space="preserve">게시 채널 목록 전용 레이어가 확인되지 않음</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel/pop.order_exchange_request_invoice.html</t>
+          <t xml:space="preserve">channel/pop.product_own_publication_channel.html</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel.sub04.inc.pop_order_exchange</t>
+          <t xml:space="preserve">channel.sub02.product_own 계열</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 배송 송장 수정 action 보강/검증</t>
+          <t xml:space="preserve">게시 채널 확인 레이어 보강</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">배송사/송장번호 수정 CRUD 필요</t>
+          <t xml:space="preserve">상품이 어느 Shop 채널에 게시되었는지 운영자가 확인해야 함</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-08-01-3</t>
+          <t xml:space="preserve">RF-02-05-02-6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1160,22 +1161,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">정산 관리</t>
+          <t xml:space="preserve">상품 등록/수정</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">정산 엑셀 상세 표시 화면</t>
+          <t xml:space="preserve">발주 담당자 찾기</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Excel/Popup</t>
+          <t xml:space="preserve">Layer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ver3.0 개정 이력 추가 항목</t>
+          <t xml:space="preserve">상품 등록 화면 하위 발주 담당자 검색/선택</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1185,7 +1186,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">확인/보강필요</t>
+          <t xml:space="preserve">보강필요</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1195,39 +1196,39 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 상세/CSV export는 있으나 스토리보드의 엑셀 상세 컬럼과 완전 동일한지 최종 대조 필요</t>
+          <t xml:space="preserve">상품 등록/수정 화면은 있으나 전용 발주 담당자 찾기 Layer는 명확하지 않음</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">스토리보드 추가 항목</t>
+          <t xml:space="preserve">channel/pop.product_own_update_order_manager.html</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel.settlement.view / admin.settlements.export</t>
+          <t xml:space="preserve">channel.sub02.product_base_edit</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">정산 상세 엑셀 컬럼 순서와 산식 검증, 필요 시 xlsx 출력 보강</t>
+          <t xml:space="preserve">발주 담당자 검색/선택 레이어 또는 동등 UI 보강</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ver3.0에서 새로 추가된 항목. 단순 화면 존재 여부가 아니라 정산 컬럼/산식 일치가 중요</t>
+          <t xml:space="preserve">발주사 연동을 위해 상품별 발주 담당자 지정 흐름 필요</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-08-01-4</t>
+          <t xml:space="preserve">RF-02-06-02-5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1237,22 +1238,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">정산 관리</t>
+          <t xml:space="preserve">공동구매 관리</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">추가 배송비 엑셀 상세 표시 화면</t>
+          <t xml:space="preserve">발주 담당자 찾기</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Excel/Popup</t>
+          <t xml:space="preserve">Popup</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ver3.0 개정 이력 추가 항목</t>
+          <t xml:space="preserve">공동구매 등록 화면 하위 발주 담당자 검색/선택</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1262,7 +1263,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">확인/보강필요</t>
+          <t xml:space="preserve">보강필요</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1272,64 +1273,64 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">추가 배송비 export route는 있으나 스토리보드 예시 컬럼과 xlsx 형식 여부 확인 필요</t>
+          <t xml:space="preserve">공동구매 등록/수정은 있으나 발주 담당자 찾기 전용 팝업은 명확하지 않음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">스토리보드 추가 항목</t>
+          <t xml:space="preserve">FileMap Page Path 공란 / Popup</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin.settlements.extra_shipping.export</t>
+          <t xml:space="preserve">channel.joint_purchase.create/edit</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">추가 배송비 상세 엑셀 컬럼/데이터 기준 최종 검증</t>
+          <t xml:space="preserve">공동구매용 발주 담당자 검색/선택 팝업 또는 동등 UI 보강</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">반품/교환 추가 배송비는 정산과 별도 상세가 필요</t>
+          <t xml:space="preserve">공동구매 상품도 발주 담당자와 연결되어야 발주사 흐름이 자연스러움</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03-01-02</t>
+          <t xml:space="preserve">RF-02-07-05-2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 채널</t>
+          <t xml:space="preserve">채널 관리자</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">접속화면</t>
+          <t xml:space="preserve">주문 관리</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">로그인 화면</t>
+          <t xml:space="preserve">반품 보류</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Web Page</t>
+          <t xml:space="preserve">Layer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 채널 로고가 들어간 전용 로그인 화면</t>
+          <t xml:space="preserve">반품 주문 상세 하위 액션</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1339,7 +1340,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규필요 또는 정책확정</t>
+          <t xml:space="preserve">보강필요</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1349,64 +1350,64 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 Shop 전용 로그인 route/view 없음. 공통 회원 로그인으로 대체 중</t>
+          <t xml:space="preserve">반품 팝업 UI는 있으나 보류 상태 전환 action/사유 입력 흐름은 별도 검증 필요</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop/login.html</t>
+          <t xml:space="preserve">channel/pop.order_return_request_pending.html</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">front.member.login 공통 화면</t>
+          <t xml:space="preserve">channel.sub04.inc.pop_order_return</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 전용 로그인 페이지가 실제 필요하면 신규 산출 필요</t>
+          <t xml:space="preserve">반품 보류 상태 변경, 사유 입력, 저장 action 보강/검증</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">스토리보드에는 Shop 채널 영역의 독립 로그인 화면으로 존재</t>
+          <t xml:space="preserve">주문 상태 흐름상 단순 표시가 아니라 상태 전환이 필요</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03-02-01</t>
+          <t xml:space="preserve">RF-02-07-05-3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 채널</t>
+          <t xml:space="preserve">채널 관리자</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">간편회원 가입</t>
+          <t xml:space="preserve">주문 관리</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">간편회원 가입절차 화면</t>
+          <t xml:space="preserve">반품 송장 수정</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Web Page</t>
+          <t xml:space="preserve">Layer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 채널 진입 중 간편가입 흐름</t>
+          <t xml:space="preserve">반품 주문 상세 하위 액션</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1416,7 +1417,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규필요 또는 정책확정</t>
+          <t xml:space="preserve">보강필요</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1426,64 +1427,64 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">공통 social_join은 있으나 Shop 전용 화면/복귀 흐름은 없음</t>
+          <t xml:space="preserve">반품 송장 수정 UI/action의 1:1 매칭 검증 필요</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop/social_join.html</t>
+          <t xml:space="preserve">channel/pop.order_return_request_invoice.html</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">front.member.social_join 공통 화면</t>
+          <t xml:space="preserve">channel.sub04.inc.pop_order_return</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 전용 간편가입 페이지 또는 공통 화면 재사용 정책 확정</t>
+          <t xml:space="preserve">반품 회수/재배송 송장 수정 action 보강/검증</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve">스토리보드는 RF-03 전용 화면으로 표시</t>
+          <t xml:space="preserve">배송사/송장번호 수정 CRUD 필요</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03-04-02-4</t>
+          <t xml:space="preserve">RF-02-07-06-2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 채널</t>
+          <t xml:space="preserve">채널 관리자</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">상품영역</t>
+          <t xml:space="preserve">주문 관리</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">상품 Q&amp;A &gt; 상품 문의하기</t>
+          <t xml:space="preserve">교환 회수 전 보류</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Popup</t>
+          <t xml:space="preserve">Layer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">상품 상세 문의 등록 팝업</t>
+          <t xml:space="preserve">교환 주문 상세 하위 액션</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1493,7 +1494,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규필요</t>
+          <t xml:space="preserve">보강필요</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1503,64 +1504,64 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 상품 상세에 문의 등록 팝업/action이 확인되지 않음</t>
+          <t xml:space="preserve">교환 보류 UI는 있으나 회수 전 상태 전환 action 검증 필요</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop/pop.product_view_contact_us.html</t>
+          <t xml:space="preserve">channel/pop.order_exchange_request_hold_before.html</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop.product_details</t>
+          <t xml:space="preserve">channel.sub04.inc.pop_order_exchange</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t xml:space="preserve">상품 문의 팝업 및 문의 저장 action</t>
+          <t xml:space="preserve">교환 회수 전 보류 상태/사유 저장 보강</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용자-채널관리자 문의 연동에 필요</t>
+          <t xml:space="preserve">교환 상태 전이가 여러 단계로 분리됨</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03-04-03</t>
+          <t xml:space="preserve">RF-02-07-06-6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 채널</t>
+          <t xml:space="preserve">채널 관리자</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">상품영역</t>
+          <t xml:space="preserve">주문 관리</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">장바구니 &gt; 옵션 변경</t>
+          <t xml:space="preserve">교환 회수 후 보류</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Popup</t>
+          <t xml:space="preserve">Layer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">장바구니 상품 옵션 변경 팝업</t>
+          <t xml:space="preserve">교환 주문 상세 하위 액션</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1570,7 +1571,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규필요</t>
+          <t xml:space="preserve">보강필요</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1580,64 +1581,64 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 Shop cart는 삭제/주문 중심이며 옵션 변경 action 없음</t>
+          <t xml:space="preserve">교환 회수 후 보류 상태 전환 action 검증 필요</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop/pop.shopping_basket_option.html</t>
+          <t xml:space="preserve">channel/pop.order_exchange_request_hold_after.html</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">front.shop.cart</t>
+          <t xml:space="preserve">channel.sub04.inc.pop_order_exchange</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t xml:space="preserve">장바구니 옵션 변경 팝업 및 update action</t>
+          <t xml:space="preserve">교환 회수 후 보류 상태/사유 저장 보강</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve">장바구니 CRUD 중 Update 기능에 해당</t>
+          <t xml:space="preserve">회수 전/후 보류가 스토리보드에서 분리됨</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03-04-06</t>
+          <t xml:space="preserve">RF-02-07-06-8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 채널</t>
+          <t xml:space="preserve">채널 관리자</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">상품영역</t>
+          <t xml:space="preserve">주문 관리</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">구매내역 확인</t>
+          <t xml:space="preserve">교환 옵션 변경</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Web Page</t>
+          <t xml:space="preserve">Layer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 완료 후/회원 구매내역 확인 화면</t>
+          <t xml:space="preserve">교환 주문 상세 하위 액션</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1647,7 +1648,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규필요</t>
+          <t xml:space="preserve">보강필요</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1657,64 +1658,64 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">전용 purchase_history route/view 없음</t>
+          <t xml:space="preserve">교환 옵션 변경 저장 action의 1:1 매칭 검증 필요</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop/purchase_history.html</t>
+          <t xml:space="preserve">channel/pop.order_exchange_request_option.html</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">없음</t>
+          <t xml:space="preserve">channel.sub04.inc.pop_order_exchange</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">구매내역 목록 페이지 신규</t>
+          <t xml:space="preserve">교환 상품 옵션 변경 UI/action 보강</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 완료 후 상세/목록 확인 흐름에 필요</t>
+          <t xml:space="preserve">교환 대상 옵션 변경은 주문상품 데이터 수정과 연결됨</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03-05-01</t>
+          <t xml:space="preserve">RF-02-07-06-9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 채널</t>
+          <t xml:space="preserve">채널 관리자</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문영역</t>
+          <t xml:space="preserve">주문 관리</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 조회 화면</t>
+          <t xml:space="preserve">교환 송장 수정</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Web Page</t>
+          <t xml:space="preserve">Layer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 주문번호/연락처 등 조회 입력 화면</t>
+          <t xml:space="preserve">교환 주문 상세 하위 액션</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1724,7 +1725,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규필요</t>
+          <t xml:space="preserve">보강필요</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1734,64 +1735,64 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">운영 route 없음. shop/sub/order_confirm 샘플은 라우팅되지 않음</t>
+          <t xml:space="preserve">교환 송장 수정 UI/action의 1:1 매칭 검증 필요</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop/order_confirm.html</t>
+          <t xml:space="preserve">channel/pop.order_exchange_request_invoice.html</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">샘플 Blade만 존재: resources/views/shop/sub/order_confirm.blade.php</t>
+          <t xml:space="preserve">channel.sub04.inc.pop_order_exchange</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 주문조회 입력 페이지 신규 또는 비회원 주문조회와 통합 라우트 연결</t>
+          <t xml:space="preserve">교환 배송 송장 수정 action 보강/검증</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t xml:space="preserve">샘플 파일은 운영 연결이 아니므로 실제 산출물로 볼 수 없음</t>
+          <t xml:space="preserve">배송사/송장번호 수정 CRUD 필요</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03-05-02-1</t>
+          <t xml:space="preserve">RF-02-08-01-3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 채널</t>
+          <t xml:space="preserve">채널 관리자</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문영역</t>
+          <t xml:space="preserve">정산 관리</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 &gt; 판매자 문의하기</t>
+          <t xml:space="preserve">정산 엑셀 상세 표시 화면</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Popup</t>
+          <t xml:space="preserve">Excel/Popup</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 상세 판매자 문의 팝업</t>
+          <t xml:space="preserve">Ver3.0 개정 이력 추가 항목</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1801,7 +1802,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규필요</t>
+          <t xml:space="preserve">확인/보강필요</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1811,64 +1812,64 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 주문 상세에 판매자 문의 저장 action이 확인되지 않음</t>
+          <t xml:space="preserve">현재 상세/CSV export는 있으나 스토리보드의 엑셀 상세 컬럼과 완전 동일한지 최종 대조 필요</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop/pop.order_details_contact_us.html</t>
+          <t xml:space="preserve">스토리보드 추가 항목</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">front.shop.order_details</t>
+          <t xml:space="preserve">channel.settlement.view / admin.settlements.export</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t xml:space="preserve">판매자 문의 팝업 및 문의 저장 action</t>
+          <t xml:space="preserve">정산 상세 엑셀 컬럼 순서와 산식 검증, 필요 시 xlsx 출력 보강</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 기준 사용자-채널관리자 문의 연동 필요</t>
+          <t xml:space="preserve">Ver3.0에서 새로 추가된 항목. 단순 화면 존재 여부가 아니라 정산 컬럼/산식 일치가 중요</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03-05-02-2</t>
+          <t xml:space="preserve">RF-02-08-01-4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 채널</t>
+          <t xml:space="preserve">채널 관리자</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문영역</t>
+          <t xml:space="preserve">정산 관리</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 &gt; 취소 신청하기</t>
+          <t xml:space="preserve">추가 배송비 엑셀 상세 표시 화면</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Popup</t>
+          <t xml:space="preserve">Excel/Popup</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 상세 취소 신청 팝업</t>
+          <t xml:space="preserve">Ver3.0 개정 이력 추가 항목</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1878,7 +1879,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">보강필요</t>
+          <t xml:space="preserve">확인/보강필요</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1888,39 +1889,39 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 item status POST는 있으나 사유 입력형 팝업은 없음</t>
+          <t xml:space="preserve">추가 배송비 export route는 있으나 스토리보드 예시 컬럼과 xlsx 형식 여부 확인 필요</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop/pop.order_details_cancel_request.html</t>
+          <t xml:space="preserve">스토리보드 추가 항목</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">front.shop.order_details / front.shop.order.item.status</t>
+          <t xml:space="preserve">admin.settlements.extra_shipping.export</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t xml:space="preserve">취소 신청 사유 입력 팝업 및 claim 저장 방식 보강</t>
+          <t xml:space="preserve">추가 배송비 상세 엑셀 컬럼/데이터 기준 최종 검증</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve">스토리보드상 즉시 처리 버튼이 아니라 신청 팝업</t>
+          <t xml:space="preserve">반품/교환 추가 배송비는 정산과 별도 상세가 필요</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03-05-02-3</t>
+          <t xml:space="preserve">RF-03-01-02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1930,22 +1931,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문영역</t>
+          <t xml:space="preserve">접속화면</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 &gt; 반품 신청하기</t>
+          <t xml:space="preserve">로그인 화면</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Popup</t>
+          <t xml:space="preserve">Web Page</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 상세 반품 신청 팝업</t>
+          <t xml:space="preserve">Shop 채널 로고가 들어간 전용 로그인 화면</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1955,7 +1956,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">보강필요</t>
+          <t xml:space="preserve">신규필요 또는 정책확정</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1965,39 +1966,39 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 item status POST는 있으나 반품 사유/회수정보 입력 팝업은 없음</t>
+          <t xml:space="preserve">현재 Shop 전용 로그인 route/view 없음. 공통 회원 로그인으로 대체 중</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop/pop.order_details_return_request.html</t>
+          <t xml:space="preserve">shop/login.html</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">front.shop.order_details / front.shop.order.item.status</t>
+          <t xml:space="preserve">front.member.login 공통 화면</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t xml:space="preserve">반품 신청 팝업 및 claim 저장 방식 보강</t>
+          <t xml:space="preserve">Shop 전용 로그인 페이지가 실제 필요하면 신규 산출 필요</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t xml:space="preserve">반품은 사유와 회수/배송 정보가 필요</t>
+          <t xml:space="preserve">스토리보드에는 Shop 채널 영역의 독립 로그인 화면으로 존재</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03-05-02-4</t>
+          <t xml:space="preserve">RF-03-02-01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2007,22 +2008,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문영역</t>
+          <t xml:space="preserve">간편회원 가입</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 &gt; 교환 신청하기</t>
+          <t xml:space="preserve">간편회원 가입절차 화면</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Popup</t>
+          <t xml:space="preserve">Web Page</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 상세 교환 신청 팝업</t>
+          <t xml:space="preserve">Shop 채널 진입 중 간편가입 흐름</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2032,7 +2033,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">보강필요</t>
+          <t xml:space="preserve">신규필요 또는 정책확정</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2042,39 +2043,39 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 item status POST는 있으나 교환 옵션/회수정보 입력 팝업은 없음</t>
+          <t xml:space="preserve">공통 social_join은 있으나 Shop 전용 화면/복귀 흐름은 없음</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop/pop.order_details_exchange_request.html</t>
+          <t xml:space="preserve">shop/social_join.html</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">front.shop.order_details / front.shop.order.item.status</t>
+          <t xml:space="preserve">front.member.social_join 공통 화면</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 신청 팝업 및 claim 저장 방식 보강</t>
+          <t xml:space="preserve">Shop 전용 간편가입 페이지 또는 공통 화면 재사용 정책 확정</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환은 옵션/회수/재배송 정보가 필요</t>
+          <t xml:space="preserve">스토리보드는 RF-03 전용 화면으로 표시</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03-05-02-5</t>
+          <t xml:space="preserve">RF-03-04-02-4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2084,12 +2085,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문영역</t>
+          <t xml:space="preserve">상품영역</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 &gt; 구매 확정하기</t>
+          <t xml:space="preserve">상품 Q&amp;A &gt; 상품 문의하기</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2099,7 +2100,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">구매확정 확인 팝업</t>
+          <t xml:space="preserve">상품 상세 문의 등록 팝업</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2109,7 +2110,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">보강필요</t>
+          <t xml:space="preserve">신규필요</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2119,39 +2120,39 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 item status POST는 있으나 확인 팝업/확정일 표시 흐름 확인 필요</t>
+          <t xml:space="preserve">Shop 상품 상세에 문의 등록 팝업/action이 확인되지 않음</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop/pop.order_details_purchase_confirm.html</t>
+          <t xml:space="preserve">shop/pop.product_view_contact_us.html</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">front.shop.order_details / front.shop.order.item.status</t>
+          <t xml:space="preserve">shop.product_details</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">구매확정 확인 레이어 및 상태 반영 검증</t>
+          <t xml:space="preserve">상품 문의 팝업 및 문의 저장 action</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve">구매확정은 정산 생성 기준이므로 UX/상태 반영 중요</t>
+          <t xml:space="preserve">사용자-채널관리자 문의 연동에 필요</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03-05-06</t>
+          <t xml:space="preserve">RF-03-04-03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2161,22 +2162,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문영역</t>
+          <t xml:space="preserve">상품영역</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 상세 화면</t>
+          <t xml:space="preserve">장바구니 &gt; 옵션 변경</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Web Page</t>
+          <t xml:space="preserve">Popup</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문 상세 보기 전용 화면</t>
+          <t xml:space="preserve">장바구니 상품 옵션 변경 팝업</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2186,7 +2187,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규/보강필요</t>
+          <t xml:space="preserve">신규필요</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2196,39 +2197,39 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 /shop/order/details는 최근 주문 1건 중심이고 주문 ID 기반 상세 분리 없음</t>
+          <t xml:space="preserve">현재 Shop cart는 삭제/주문 중심이며 옵션 변경 action 없음</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop/order_details_view.html</t>
+          <t xml:space="preserve">shop/pop.shopping_basket_option.html</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">front.shop.order_details</t>
+          <t xml:space="preserve">front.shop.cart</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문번호/ID 기반 상세 화면 분리 또는 기존 화면 확장</t>
+          <t xml:space="preserve">장바구니 옵션 변경 팝업 및 update action</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve">구매내역/주문조회에서 특정 주문 상세로 이동해야 함</t>
+          <t xml:space="preserve">장바구니 CRUD 중 Update 기능에 해당</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03-05-03</t>
+          <t xml:space="preserve">RF-03-04-06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2238,12 +2239,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문영역</t>
+          <t xml:space="preserve">상품영역</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">취소 주문 목록</t>
+          <t xml:space="preserve">구매내역 확인</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2253,7 +2254,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">취소 목록 화면</t>
+          <t xml:space="preserve">주문 완료 후/회원 구매내역 확인 화면</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2263,7 +2264,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">보강필요</t>
+          <t xml:space="preserve">신규필요</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2273,39 +2274,39 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">front/shop/cancel_details.blade.php는 존재하지만 정적 샘플 성격. 실제 claim 데이터 연결 필요</t>
+          <t xml:space="preserve">전용 purchase_history route/view 없음</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop/cancel_details.html</t>
+          <t xml:space="preserve">shop/purchase_history.html</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">front.shop.cancel.details</t>
+          <t xml:space="preserve">없음</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t xml:space="preserve">취소 주문 목록을 실제 OrderClaim/OrdersProduct 기준으로 재작업</t>
+          <t xml:space="preserve">구매내역 목록 페이지 신규</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t xml:space="preserve">파일 존재만으로 완료 처리하면 운영 데이터가 보이지 않을 수 있음</t>
+          <t xml:space="preserve">주문 완료 후 상세/목록 확인 흐름에 필요</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03-05-04</t>
+          <t xml:space="preserve">RF-03-05-01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2320,7 +2321,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">반품 주문 목록</t>
+          <t xml:space="preserve">주문 조회 화면</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2330,7 +2331,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">반품 목록 화면</t>
+          <t xml:space="preserve">Shop 주문번호/연락처 등 조회 입력 화면</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2340,7 +2341,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">보강필요</t>
+          <t xml:space="preserve">신규필요</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2350,39 +2351,39 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">front/shop/return_details.blade.php는 존재하지만 정적 샘플 성격. 실제 claim 데이터 연결 필요</t>
+          <t xml:space="preserve">운영 route 없음. shop/sub/order_confirm 샘플은 라우팅되지 않음</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop/return_details.html</t>
+          <t xml:space="preserve">shop/order_confirm.html</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">front.shop.return.details</t>
+          <t xml:space="preserve">샘플 Blade만 존재: resources/views/shop/sub/order_confirm.blade.php</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t xml:space="preserve">반품 주문 목록을 실제 claim 데이터 기준으로 재작업</t>
+          <t xml:space="preserve">Shop 주문조회 입력 페이지 신규 또는 비회원 주문조회와 통합 라우트 연결</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve">파일 존재만으로 완료 처리하면 운영 데이터가 보이지 않을 수 있음</t>
+          <t xml:space="preserve">샘플 파일은 운영 연결이 아니므로 실제 산출물로 볼 수 없음</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03-05-05</t>
+          <t xml:space="preserve">RF-03-05-02-1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2397,17 +2398,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 주문 목록</t>
+          <t xml:space="preserve">주문 &gt; 판매자 문의하기</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Web Page</t>
+          <t xml:space="preserve">Popup</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 목록 화면</t>
+          <t xml:space="preserve">주문 상세 판매자 문의 팝업</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2417,7 +2418,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">보강필요</t>
+          <t xml:space="preserve">신규필요</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2427,39 +2428,39 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">front/shop/exchange_details.blade.php는 존재하지만 정적 샘플 성격. 실제 claim 데이터 연결 필요</t>
+          <t xml:space="preserve">Shop 주문 상세에 판매자 문의 저장 action이 확인되지 않음</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop/exchange_details.html</t>
+          <t xml:space="preserve">shop/pop.order_details_contact_us.html</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">front.shop.exchange.details</t>
+          <t xml:space="preserve">front.shop.order_details</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t xml:space="preserve">교환 주문 목록을 실제 claim 데이터 기준으로 재작업</t>
+          <t xml:space="preserve">판매자 문의 팝업 및 문의 저장 action</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve">파일 존재만으로 완료 처리하면 운영 데이터가 보이지 않을 수 있음</t>
+          <t xml:space="preserve">주문 기준 사용자-채널관리자 문의 연동 필요</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03-06-02</t>
+          <t xml:space="preserve">RF-03-05-02-2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2469,22 +2470,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">공지사항</t>
+          <t xml:space="preserve">주문영역</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">공지사항 상세</t>
+          <t xml:space="preserve">주문 &gt; 취소 신청하기</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Web Page</t>
+          <t xml:space="preserve">Popup</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 채널 공지사항 상세 화면</t>
+          <t xml:space="preserve">주문 상세 취소 신청 팝업</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2494,7 +2495,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규필요</t>
+          <t xml:space="preserve">보강필요</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2504,54 +2505,54 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 공지 목록 route는 있으나 상세 route/view 없음</t>
+          <t xml:space="preserve">현재 item status POST는 있으나 사유 입력형 팝업은 없음</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop/notice_view.html</t>
+          <t xml:space="preserve">shop/pop.order_details_cancel_request.html</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">shop.notices 목록만 존재</t>
+          <t xml:space="preserve">front.shop.order_details / front.shop.order.item.status</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 공지사항 상세 페이지 신규</t>
+          <t xml:space="preserve">취소 신청 사유 입력 팝업 및 claim 저장 방식 보강</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve">공지 목록에서 상세 확인이 필요</t>
+          <t xml:space="preserve">스토리보드상 즉시 처리 버튼이 아니라 신청 팝업</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-04-02-01-2</t>
+          <t xml:space="preserve">RF-03-05-02-3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">발주사 페이지</t>
+          <t xml:space="preserve">Shop 채널</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">발주 관리</t>
+          <t xml:space="preserve">주문영역</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">발주 대기 보기/수정</t>
+          <t xml:space="preserve">주문 &gt; 반품 신청하기</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2561,7 +2562,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">발주 대기 상세/수정 팝업</t>
+          <t xml:space="preserve">주문 상세 반품 신청 팝업</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2581,102 +2582,718 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 발주 상세/수정은 full page 성격. 스토리보드 팝업 방식과 1:1 일치 여부 확인 필요</t>
+          <t xml:space="preserve">현재 item status POST는 있으나 반품 사유/회수정보 입력 팝업은 없음</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">purchase/pop.waiting_view.html / purchase/pop.waiting_update.html</t>
+          <t xml:space="preserve">shop/pop.order_details_return_request.html</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">distributor.order_details / distributor.order.update</t>
+          <t xml:space="preserve">front.shop.order_details / front.shop.order.item.status</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t xml:space="preserve">팝업 UI가 필수면 레이어/팝업 형태로 보강</t>
+          <t xml:space="preserve">반품 신청 팝업 및 claim 저장 방식 보강</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve">발주사 운영 흐름에서 목록 내 즉시 확인/수정 UX 필요</t>
+          <t xml:space="preserve">반품은 사유와 회수/배송 정보가 필요</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t xml:space="preserve">25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-03-05-02-4</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shop 채널</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주문영역</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주문 &gt; 교환 신청하기</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Popup</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주문 상세 교환 신청 팝업</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보강필요</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 item status POST는 있으나 교환 옵션/회수정보 입력 팝업은 없음</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop/pop.order_details_exchange_request.html</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">front.shop.order_details / front.shop.order.item.status</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">교환 신청 팝업 및 claim 저장 방식 보강</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">교환은 옵션/회수/재배송 정보가 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-03-05-02-5</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shop 채널</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주문영역</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주문 &gt; 구매 확정하기</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Popup</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구매확정 확인 팝업</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보강필요</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 item status POST는 있으나 확인 팝업/확정일 표시 흐름 확인 필요</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop/pop.order_details_purchase_confirm.html</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">front.shop.order_details / front.shop.order.item.status</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구매확정 확인 레이어 및 상태 반영 검증</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구매확정은 정산 생성 기준이므로 UX/상태 반영 중요</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-03-05-06</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shop 채널</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주문영역</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주문 상세 화면</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Web Page</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주문 상세 보기 전용 화면</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규/보강필요</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 /shop/order/details는 최근 주문 1건 중심이고 주문 ID 기반 상세 분리 없음</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop/order_details_view.html</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">front.shop.order_details</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주문번호/ID 기반 상세 화면 분리 또는 기존 화면 확장</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구매내역/주문조회에서 특정 주문 상세로 이동해야 함</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-03-05-03</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shop 채널</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주문영역</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">취소 주문 목록</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Web Page</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">취소 목록 화면</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보강필요</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">front/shop/cancel_details.blade.php는 존재하지만 정적 샘플 성격. 실제 claim 데이터 연결 필요</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop/cancel_details.html</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">front.shop.cancel.details</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">취소 주문 목록을 실제 OrderClaim/OrdersProduct 기준으로 재작업</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">파일 존재만으로 완료 처리하면 운영 데이터가 보이지 않을 수 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-03-05-04</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shop 채널</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주문영역</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반품 주문 목록</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Web Page</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반품 목록 화면</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보강필요</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">front/shop/return_details.blade.php는 존재하지만 정적 샘플 성격. 실제 claim 데이터 연결 필요</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop/return_details.html</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">front.shop.return.details</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반품 주문 목록을 실제 claim 데이터 기준으로 재작업</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">파일 존재만으로 완료 처리하면 운영 데이터가 보이지 않을 수 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-03-05-05</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shop 채널</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주문영역</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">교환 주문 목록</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Web Page</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">교환 목록 화면</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보강필요</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">front/shop/exchange_details.blade.php는 존재하지만 정적 샘플 성격. 실제 claim 데이터 연결 필요</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop/exchange_details.html</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">front.shop.exchange.details</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">교환 주문 목록을 실제 claim 데이터 기준으로 재작업</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">파일 존재만으로 완료 처리하면 운영 데이터가 보이지 않을 수 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-03-06-02</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shop 채널</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공지사항</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공지사항 상세</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Web Page</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shop 채널 공지사항 상세 화면</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규필요</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shop 공지 목록 route는 있으나 상세 route/view 없음</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop/notice_view.html</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop.notices 목록만 존재</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shop 공지사항 상세 페이지 신규</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공지 목록에서 상세 확인이 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-04-02-01-2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발주사 페이지</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발주 관리</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발주 대기 보기/수정</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Popup</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발주 대기 상세/수정 팝업</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보강필요</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 발주 상세/수정은 full page 성격. 스토리보드 팝업 방식과 1:1 일치 여부 확인 필요</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">purchase/pop.waiting_view.html / purchase/pop.waiting_update.html</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">distributor.order_details / distributor.order.update</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">팝업 UI가 필수면 레이어/팝업 형태로 보강</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발주사 운영 흐름에서 목록 내 즉시 확인/수정 UX 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t xml:space="preserve">33</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t xml:space="preserve">RF-04-02-02-1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t xml:space="preserve">발주사 페이지</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t xml:space="preserve">발주 관리</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t xml:space="preserve">발주 완료 보기/수정</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t xml:space="preserve">Popup</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">발주 완료 상세/수정 팝업</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-07-28</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">보강필요</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+      <c r="J42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t xml:space="preserve">현재 발주 상세/수정은 full page 성격. 스토리보드 팝업 방식과 1:1 일치 여부 확인 필요</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">purchase/pop.completed_view.html / purchase/pop.completed_update.html</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">distributor.order_details / distributor.order.update</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t xml:space="preserve">팝업 UI가 필수면 레이어/팝업 형태로 보강</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t xml:space="preserve">배송 전 수정 가능 조건 등 상태별 제어 필요</t>
         </is>
@@ -2690,12 +3307,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="24" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
@@ -2787,7 +3404,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2817,7 +3434,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">스토리보드상 대표 이미지/회사 소개/이용방법/공지/회사정보가 있는 메인 화면</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2827,7 +3444,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구현확인</t>
+          <t xml:space="preserve">신규/재작업필요</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -2837,7 +3454,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 Laravel route/view 존재. 신규 파일 대상 아님</t>
+          <t xml:space="preserve">현재 resources/views/front/index.blade.php는 container 내부가 비어 있으며 “me9market/main/index.php 소스, container 내부는 비어 있었음” 주석만 존재</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -2847,44 +3464,44 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">front.index / /</t>
+          <t xml:space="preserve">/ route -&gt; front.index</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규 파일 불필요</t>
+          <t xml:space="preserve">홈페이지 메인 실제 퍼블리싱/콘텐츠/공지 추출/회사정보 영역 구현 필요</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FileMap은 파일요청중이나 현재 운영 화면 존재</t>
+          <t xml:space="preserve">파일 존재만으로 구현 완료로 볼 수 없음. 인덱스 누락 항목</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-01-02</t>
+          <t xml:space="preserve">RF-02-02-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">홈페이지</t>
+          <t xml:space="preserve">채널 관리자</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">서비스안내</t>
+          <t xml:space="preserve">대시보드</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">서비스 안내</t>
+          <t xml:space="preserve">대시보드 구성화면</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2894,7 +3511,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">채널관리자 첫 화면. 주문단계, 회원정보, 문의사항, 주문목록, 방문 채널 등 표시</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2904,7 +3521,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">구현확인</t>
+          <t xml:space="preserve">구현확인/추가검수</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -2914,54 +3531,54 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 Laravel route/view 존재</t>
+          <t xml:space="preserve">channel/index.blade.php는 실제 counts/recentOrders/recentInquiries를 사용하나 스토리보드의 바로가기 메뉴/서브관리 채널목록 등 일부 항목은 최종 검수 필요</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">/homepage/company/service.html</t>
+          <t xml:space="preserve">channel/dashboard.html</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">front.pages.service / /service</t>
+          <t xml:space="preserve">/channel -&gt; channel.index</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규 파일 불필요</t>
+          <t xml:space="preserve">운영 데이터 연동은 있음. 스토리보드 구성요소 빠짐 여부 추가 검수</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">인덱스성 화면이므로 별도 추적 필요</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-01-03</t>
+          <t xml:space="preserve">RF-05-02-01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">홈페이지</t>
+          <t xml:space="preserve">전체관리자</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">주요기능</t>
+          <t xml:space="preserve">대시보드</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">주요기능 소개</t>
+          <t xml:space="preserve">전체관리자 대시보드 구성화면</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2971,7 +3588,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">전체관리자 첫 화면. 블록 조합형 대시보드, 주문상태, 매출 Top20, 카테고리 Top20, 현황 리스트</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2981,7 +3598,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">구현확인</t>
+          <t xml:space="preserve">재작업필요</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -2991,54 +3608,54 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 Laravel route/view 존재</t>
+          <t xml:space="preserve">admin/dashboard.blade.php는 16/5/1/0/5/2/3, 0000-00-00, Red/Blue 차트 등 하드코딩 샘플이 남아 있음. AdminController가 넘기는 counts도 화면에서 사용하지 않음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve">/homepage/company/features.html</t>
+          <t xml:space="preserve">FileMap Page Path 공란 / master main 참조</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">front.pages.features / /features</t>
+          <t xml:space="preserve">/admin/dashboard -&gt; admin.dashboard</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규 파일 불필요</t>
+          <t xml:space="preserve">실제 주문/매출/카테고리/회원/신고/포인트 데이터 연동 대시보드로 재작업</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">이전 산출물에서 가장 크게 누락된 인덱스 항목</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-01-04</t>
+          <t xml:space="preserve">RF-05-02-01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">홈페이지</t>
+          <t xml:space="preserve">전체관리자</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">가입안내</t>
+          <t xml:space="preserve">대시보드</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">가입 안내</t>
+          <t xml:space="preserve">master/index 샘플 화면</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3048,7 +3665,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">전체관리자 대시보드와 유사한 샘플 파일</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3058,7 +3675,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">구현확인</t>
+          <t xml:space="preserve">정리필요</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3068,64 +3685,64 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 Laravel route/view 존재</t>
+          <t xml:space="preserve">resources/views/master/index.blade.php는 Channel A/user01/Reporter X/Red Blue 등 샘플 데이터. 실제 MasterController@index는 admin.dashboard로 redirect하므로 운영 route에서 사용되지 않음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">/homepage/company/subscription_information.html</t>
+          <t xml:space="preserve">Physical File 참조: master/main</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">front.pages.subscription_info</t>
+          <t xml:space="preserve">/master -&gt; admin.dashboard redirect</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규 파일 불필요</t>
+          <t xml:space="preserve">운영 미사용 샘플이면 제거 또는 FileMap상 패턴 참고 파일로 명확히 분리</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">현재 파일만 보면 구현된 것처럼 오판 가능</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-01-06-01~02-5</t>
+          <t xml:space="preserve">RF-05-02-02~11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">홈페이지</t>
+          <t xml:space="preserve">전체관리자</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">주문조회</t>
+          <t xml:space="preserve">디자인 패턴</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">비회원 주문조회/상세/클레임/문의</t>
+          <t xml:space="preserve">admin/sub*, master/sub* 패턴/샘플 화면</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Page/Popup</t>
+          <t xml:space="preserve">Page/Layer/Popup</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">일반 리스트, 보기, 입력, 팝업, 레이어, 로딩 패턴</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3135,7 +3752,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">구현확인/UX검수</t>
+          <t xml:space="preserve">임시/패턴파일</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -3145,64 +3762,64 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">비회원 주문조회 route와 상세/claim/inquiry action 존재</t>
+          <t xml:space="preserve">admin/sub01, sub02, sub03, view, newpage, layer_large 및 master/sub01~03은 홍길동/111111/테스트 내용/내용노출 등 샘플 데이터가 다수 남아 있음</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">/homepage/order/general_order_confirm.html 등</t>
+          <t xml:space="preserve">/admin/sub01, /admin/sub02, /admin/sub03, /admin/view, /admin/newpage, /admin/loading</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">front.nonmember.order_check / front.nonmember.order_details</t>
+          <t xml:space="preserve">admin.sub.* / master.sub* redirect</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규 파일보다 레이어 UX만 필요 시 보강</t>
+          <t xml:space="preserve">운영 CRUD 화면으로 오해하지 않도록 패턴 파일로 분리 표기. 실제 전체관리자 업무화면은 별도 구현 필요</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">스토리보드 디자인 패턴용이면 완료 기준이 다르고, 운영 메뉴에 노출되면 문제</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-01-07-09~17</t>
+          <t xml:space="preserve">RF-03-05-01~05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">홈페이지/마이페이지</t>
+          <t xml:space="preserve">Shop 채널</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">회원영역</t>
+          <t xml:space="preserve">주문영역</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">대시보드/프로필/배송지/방문채널/포인트/장바구니/찜</t>
+          <t xml:space="preserve">shop/sub 주문 샘플 파일</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Page/Layer</t>
+          <t xml:space="preserve">Page</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Shop 주문확인/상세/취소/반품/교환 샘플 파일</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3212,7 +3829,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">구현확인</t>
+          <t xml:space="preserve">운영미연결/재작업필요</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3222,136 +3839,141 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">마이페이지 주요 route/view 존재</t>
+          <t xml:space="preserve">resources/views/shop/sub/*.blade.php는 상품명 111111 등 정적 샘플이고 현재 운영 route는 front/shop/*를 사용함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">/homepage/mypage/*.html</t>
+          <t xml:space="preserve">shop/order_confirm.html, order_details.html, cancel_details.html 등</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">mypage.dashboard/profile/delivery/visited/points/cart/wishlist</t>
+          <t xml:space="preserve">운영 route 미연결 샘플</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규 파일 불필요. 스타일/액션 회귀검수 대상</t>
+          <t xml:space="preserve">운영 Shop 주문 화면은 front/shop 쪽으로 실제 데이터 연결 필요. shop/sub는 샘플/참고로 분리</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">샘플 파일 존재 때문에 완료로 판단하면 안 됨</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-01~04</t>
+          <t xml:space="preserve">RF-03-04-03~05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">채널 관리자</t>
+          <t xml:space="preserve">Shop 채널</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">로그인/대시보드/정보관리/Shop 관리</t>
+          <t xml:space="preserve">상품영역</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Page/Layer</t>
+          <t xml:space="preserve">front/cart, checkout, payment index</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Page</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-28</t>
+          <t xml:space="preserve">기존 쇼핑몰 템플릿 계열 화면</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">구현확인</t>
+          <t xml:space="preserve">2026-07-28</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">중복/정리필요</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">채널관리자 주요 route/view 존재</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel/*.html</t>
+          <t xml:space="preserve">front/cart/index, front/checkout/index, front/payment/index는 기존 일반 쇼핑몰 템플릿 성격이고 Shop 채널 운영 흐름은 front/shop/cart/order_form/order_complete와 분리됨</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel.login/index/settings/shop_*</t>
+          <t xml:space="preserve">기획 FileMap 직접 경로 아님</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규 파일 불필요. 비공개 인원관리/SMS는 별도 보강</t>
+          <t xml:space="preserve">front.cart/payment/checkout legacy</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">운영에 사용할 화면과 미사용 템플릿을 명확히 분리</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중복 화면이 있으면 검수자가 실제 구현 파일을 혼동함</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-05-01~05</t>
+          <t xml:space="preserve">RF-01-07-10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">채널 관리자</t>
+          <t xml:space="preserve">홈페이지/마이페이지</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">상품 관리</t>
+          <t xml:space="preserve">회원영역</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">자사/공개/부분공개 상품 목록/등록</t>
+          <t xml:space="preserve">front/mypage/sub01/modify 샘플성 파일</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Page/Layer</t>
+          <t xml:space="preserve">Page</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">마이페이지 회원정보 수정 과거/샘플 화면</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3361,7 +3983,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">부분구현</t>
+          <t xml:space="preserve">중복/정리필요</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3371,407 +3993,27 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">상품 CRUD route/view 존재. 일부 하위 레이어는 보강 필요</t>
+          <t xml:space="preserve">운영 route는 /mypage/profile -&gt; front.mypage.profile 사용. sub01/modify는 abcde1234/홍길동 등 정적 값이 남아 있음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel/product_*.html</t>
+          <t xml:space="preserve">/homepage/mypage/member_update.html</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel.product_* / channel.product.base.*</t>
+          <t xml:space="preserve">mypage.profile이 운영 매칭</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기본 CRUD 신규 파일 불필요, 하위 Layer 보강</t>
+          <t xml:space="preserve">sub01/modify는 미사용 샘플이면 정리, 운영이면 실제 데이터/action 연결 필요</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RF-02-06-01~03</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">채널 관리자</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공동구매 관리</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공동구매 목록/등록/수정</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-07-28</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구현확인</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공동구매 route/view 존재</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공란</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">channel.joint_purchase.*</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규 파일 불필요. 발주담당자 찾기 팝업은 보강</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RF-02-07-01~09</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">채널 관리자</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">주문 관리</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">주문/취소/반품/교환 목록</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page/Layer</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-07-28</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분구현</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">주문 목록/상태 변경 route 존재. 보류/송장/옵션 레이어 action은 보강 필요</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">channel/order_*.html</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">channel.order.*</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">목록 신규 파일 불필요, 상세 액션 보강</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RF-02-08-01~02-4</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">채널/전체관리자</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정산 관리</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">채널 정산/총괄 정산/상세/집행현황</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page/Excel</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-07-28</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구현확인/정산식검수</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">채널/관리자 정산 route/view/export 존재</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스토리보드 Ver3.0 추가 항목</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">channel.settlement.* / admin.settlements.*</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신규 화면보다 컬럼/산식/xlsx 여부 검증</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이메일 정산 요구와 함께 최종 검수 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RF-04-01-01~02-02-1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">발주사 페이지</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">발주 관리</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">로그인/대기/완료/상세/수정</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page/Popup</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-07-28</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분구현</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">발주사 route/view 존재. 팝업 형태 일치 여부는 보강 대상</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">purchase/*.html</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">distributor.*</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기본 CRUD 신규 파일 불필요, 팝업 UX 보강 검토</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RF-05-01~02-11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전체관리자</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">로그인/대시보드/디자인 패턴</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page/Layer/Popup</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-07-28</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구현확인/패턴검수</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">admin 운영 화면과 master/admin 패턴 파일 존재</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FileMap Physical File 참조</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">admin.* / master.*</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정산관리 운영 화면은 admin.settlements로 구현됨</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">디자인 패턴 화면은 실제 업무 CRUD라기보다 퍼블리싱 프레임 성격</t>
+          <t xml:space="preserve">정보수정 버튼 # 문제와 연결됐던 유형</t>
         </is>
       </c>
     </row>
@@ -3783,12 +4025,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="24" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
@@ -3885,32 +4127,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-08-01</t>
+          <t xml:space="preserve">RF-01-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">채널 관리자</t>
+          <t xml:space="preserve">홈페이지</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정산 관리</t>
+          <t xml:space="preserve">main</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정산 리스트 기준</t>
+          <t xml:space="preserve">메인 페이지</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">요구사항</t>
+          <t xml:space="preserve">Web Page</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구매확정 주문 기준으로 정산 리스트 생성. 정산/미정산 상태변경 없음</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -3920,7 +4162,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">반영기준</t>
+          <t xml:space="preserve">구현확인</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -3930,27 +4172,27 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정산 완료 상태 토글이 아니라 구매확정 기준 정산 데이터와 집행현황을 보여주는 구조가 맞음</t>
+          <t xml:space="preserve">현재 Laravel route/view 존재. 신규 파일 대상 아님</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정산 메일 1번</t>
+          <t xml:space="preserve">/homepage/main/index.html</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel.settlement.list / admin.settlements</t>
+          <t xml:space="preserve">front.index / /</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정산 상태변경 UI를 만들 필요 없음</t>
+          <t xml:space="preserve">신규 파일 불필요</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">메일의 핵심 확인 사항</t>
+          <t xml:space="preserve">FileMap은 파일요청중이나 현재 운영 화면 존재</t>
         </is>
       </c>
     </row>
@@ -3962,32 +4204,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-08-02-1</t>
+          <t xml:space="preserve">RF-01-02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">전체관리자</t>
+          <t xml:space="preserve">홈페이지</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">정산 관리</t>
+          <t xml:space="preserve">서비스안내</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">정산 집행 현황 입력</t>
+          <t xml:space="preserve">서비스 안내</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">요구사항</t>
+          <t xml:space="preserve">Web Page</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">총괄관리자가 회원사/채널 정산 집행 확인용 집행일, 집행내역, 금액, 첨부자료 입력</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -4007,27 +4249,27 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SettlementExecution 계열 route가 존재함</t>
+          <t xml:space="preserve">현재 Laravel route/view 존재</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">스토리보드 Ver3.0 추가</t>
+          <t xml:space="preserve">/homepage/company/service.html</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin.settlements.executions.store/download</t>
+          <t xml:space="preserve">front.pages.service / /service</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">운영 데이터 기준 저장/노출 최종 검수</t>
+          <t xml:space="preserve">신규 파일 불필요</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">채널 정산 화면에 집행현황이 같이 노출되어야 함</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -4039,32 +4281,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-08-02-3</t>
+          <t xml:space="preserve">RF-01-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">전체관리자</t>
+          <t xml:space="preserve">홈페이지</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">정산 관리</t>
+          <t xml:space="preserve">주요기능</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">자사PG 채널 지급액 상세 표기</t>
+          <t xml:space="preserve">주요기능 소개</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">요구사항</t>
+          <t xml:space="preserve">Web Page</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">자사PG 12,500원 결제 시 Me9가 지급할 채널 지급액은 0으로 표기. 포인트 결제가 있으면 포인트 예수금 기준 금액만 별도 반영</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -4074,7 +4316,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">반영기준</t>
+          <t xml:space="preserve">구현확인</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -4084,27 +4326,27 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">스토리보드 Ver3.0 가이드상 자사PG 결제액은 Me9 정산 지급 대상이 아님</t>
+          <t xml:space="preserve">현재 Laravel route/view 존재</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve">정산 메일 2번 / 11111.png / 22222.png</t>
+          <t xml:space="preserve">/homepage/company/features.html</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin.settlements.payout</t>
+          <t xml:space="preserve">front.pages.features / /features</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">자사PG/공용PG/자사포인트/Me9포인트/상품가/배송비/정산비용 컬럼 분리 유지</t>
+          <t xml:space="preserve">신규 파일 불필요</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">많은 건수에서 혼동 방지를 위해 PG구분/상품유형/구분 필터 또는 상세 링크 필요</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -4116,32 +4358,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-08-02-4</t>
+          <t xml:space="preserve">RF-01-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">전체관리자</t>
+          <t xml:space="preserve">홈페이지</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">정산 관리</t>
+          <t xml:space="preserve">가입안내</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">채널 청구액 상세 표기</t>
+          <t xml:space="preserve">가입 안내</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">요구사항</t>
+          <t xml:space="preserve">Web Page</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SMS 수수료, 지급포인트, 매입/수수료를 채널 청구액 상세로 분리</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -4151,7 +4393,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">반영기준</t>
+          <t xml:space="preserve">구현확인</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -4161,27 +4403,27 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">청구액은 지급액과 다른 상세 목록으로 확인되어야 함</t>
+          <t xml:space="preserve">현재 Laravel route/view 존재</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">스토리보드 Ver3.0 추가</t>
+          <t xml:space="preserve">/homepage/company/subscription_information.html</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin.settlements.billing</t>
+          <t xml:space="preserve">front.pages.subscription_info</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">상세/엑셀 컬럼 및 합계 검증</t>
+          <t xml:space="preserve">신규 파일 불필요</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">자사PG 이용 시 지급포인트 제공 불가 조건 포함</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -4193,32 +4435,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-08-01-3</t>
+          <t xml:space="preserve">RF-01-06-01~02-5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">채널 관리자</t>
+          <t xml:space="preserve">홈페이지</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">정산 관리</t>
+          <t xml:space="preserve">주문조회</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">정산 엑셀 상세</t>
+          <t xml:space="preserve">비회원 주문조회/상세/클레임/문의</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">요구사항</t>
+          <t xml:space="preserve">Page/Popup</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">등록일, 주문번호, 주문유형, 상품유형, 구분, PG결제, 포인트결제, 상품가, 배송비, 할인금액, 수수료, SMS, 제공포인트, 정산비용 표시</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -4228,7 +4470,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">확인필요</t>
+          <t xml:space="preserve">구현확인/UX검수</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -4238,27 +4480,27 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재 export는 있으나 스토리보드 컬럼과 완전 동일 여부 확인 필요</t>
+          <t xml:space="preserve">비회원 주문조회 route와 상세/claim/inquiry action 존재</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">스토리보드 Ver3.0 추가</t>
+          <t xml:space="preserve">/homepage/order/general_order_confirm.html 등</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin.settlements.export</t>
+          <t xml:space="preserve">front.nonmember.order_check / front.nonmember.order_details</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">엑셀 컬럼 순서/명칭/산식 대조</t>
+          <t xml:space="preserve">신규 파일보다 레이어 UX만 필요 시 보강</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">출력 파일 확장자가 CSV면 실제 xlsx 요구 여부 결정 필요</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -4270,72 +4512,601 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-08-01-4</t>
+          <t xml:space="preserve">RF-01-07-09~17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t xml:space="preserve">홈페이지/마이페이지</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회원영역</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대시보드/프로필/배송지/방문채널/포인트/장바구니/찜</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page/Layer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구현확인</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마이페이지 주요 route/view 존재</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/homepage/mypage/*.html</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mypage.dashboard/profile/delivery/visited/points/cart/wishlist</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규 파일 불필요. 스타일/액션 회귀검수 대상</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-02-01~04</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t xml:space="preserve">채널 관리자</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로그인/대시보드/정보관리/Shop 관리</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page/Layer</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구현확인</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">채널관리자 주요 route/view 존재</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">channel/*.html</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">channel.login/index/settings/shop_*</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규 파일 불필요. 비공개 인원관리/SMS는 별도 보강</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-02-05-01~05</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">채널 관리자</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상품 관리</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자사/공개/부분공개 상품 목록/등록</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page/Layer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분구현</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상품 CRUD route/view 존재. 일부 하위 레이어는 보강 필요</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">channel/product_*.html</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">channel.product_* / channel.product.base.*</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기본 CRUD 신규 파일 불필요, 하위 Layer 보강</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-02-06-01~03</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">채널 관리자</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공동구매 관리</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공동구매 목록/등록/수정</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구현확인</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공동구매 route/view 존재</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공란</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">channel.joint_purchase.*</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규 파일 불필요. 발주담당자 찾기 팝업은 보강</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-02-07-01~09</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">채널 관리자</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주문 관리</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주문/취소/반품/교환 목록</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page/Layer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분구현</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주문 목록/상태 변경 route 존재. 보류/송장/옵션 레이어 action은 보강 필요</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">channel/order_*.html</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">channel.order.*</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목록 신규 파일 불필요, 상세 액션 보강</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-02-08-01~02-4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">채널/전체관리자</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">정산 관리</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">추가 배송비 엑셀 상세</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요구사항</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">완료일시, 반품/교환 주문번호, 원주문번호, 주문상태, 주문유형, 상품유형, 결제비용, 추가배송비 표시</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-07-28</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">확인필요</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">현재 extra shipping export는 있으나 컬럼 완전 일치 확인 필요</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스토리보드 Ver3.0 추가</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">admin.settlements.extra_shipping.export</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">추가배송비 상세 산출 기준 검증</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">반품/교환 배송비는 일반 정산과 분리 출력</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">채널 정산/총괄 정산/상세/집행현황</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page/Excel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구현확인/정산식검수</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">채널/관리자 정산 route/view/export 존재</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스토리보드 Ver3.0 추가 항목</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">channel.settlement.* / admin.settlements.*</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규 화면보다 컬럼/산식/xlsx 여부 검증</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이메일 정산 요구와 함께 최종 검수 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-04-01-01~02-02-1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발주사 페이지</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발주 관리</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로그인/대기/완료/상세/수정</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page/Popup</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분구현</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발주사 route/view 존재. 팝업 형태 일치 여부는 보강 대상</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">purchase/*.html</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">distributor.*</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기본 CRUD 신규 파일 불필요, 팝업 UX 보강 검토</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-05-01~02-11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전체관리자</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로그인/대시보드/디자인 패턴</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page/Layer/Popup</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구현확인/패턴검수</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin 운영 화면과 master/admin 패턴 파일 존재</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FileMap Physical File 참조</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin.* / master.*</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정산관리 운영 화면은 admin.settlements로 구현됨</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디자인 패턴 화면은 실제 업무 CRUD라기보다 퍼블리싱 프레임 성격</t>
         </is>
       </c>
     </row>
@@ -4347,11 +5118,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="13" max="13" width="24" customWidth="1"/>
+    <col min="14" max="14" width="24" customWidth="1"/>
+    <col min="15" max="15" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4362,22 +5143,72 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">필요 문서/결정</t>
+          <t xml:space="preserve">스토리보드 No</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">필요 이유</t>
+          <t xml:space="preserve">웹 영역</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">대상 화면 ID</t>
+          <t xml:space="preserve">스토리보드 영역</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">없을 경우 위험</t>
+          <t xml:space="preserve">스토리보드 상세명</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">페이지 종류</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추가설명</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요청일자</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">처리상태</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">처리일자</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의견</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FileMap Page Path</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 Laravel 매칭</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">실제 필요 산출물/작업</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">판단근거</t>
         </is>
       </c>
     </row>
@@ -4389,22 +5220,72 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 채널 최신 퍼블리싱 원본 또는 캡처 묶음</t>
+          <t xml:space="preserve">RF-02-08-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FileMap RF-03 대부분이 Shop 채널 별도 화면을 전제로 함</t>
+          <t xml:space="preserve">채널 관리자</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03 전체</t>
+          <t xml:space="preserve">정산 관리</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">공통 회원/주문 화면 재사용 여부를 임의 판단하게 되어 의도와 다른 화면이 될 수 있음</t>
+          <t xml:space="preserve">정산 리스트 기준</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요구사항</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구매확정 주문 기준으로 정산 리스트 생성. 정산/미정산 상태변경 없음</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반영기준</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정산 완료 상태 토글이 아니라 구매확정 기준 정산 데이터와 집행현황을 보여주는 구조가 맞음</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정산 메일 1번</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">channel.settlement.list / admin.settlements</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정산 상태변경 UI를 만들 필요 없음</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">메일의 핵심 확인 사항</t>
         </is>
       </c>
     </row>
@@ -4416,22 +5297,72 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">취소/반품/교환 상태 전이표</t>
+          <t xml:space="preserve">RF-02-08-02-1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용자 신청, 채널관리자 승인/보류/송장/옵션 변경, 발주사 흐름이 연결됨</t>
+          <t xml:space="preserve">전체관리자</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-01-06, RF-01-07-18, RF-02-07, RF-03-05</t>
+          <t xml:space="preserve">정산 관리</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태값은 저장되지만 실제 운영 흐름이 끊길 수 있음</t>
+          <t xml:space="preserve">정산 집행 현황 입력</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요구사항</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">총괄관리자가 회원사/채널 정산 집행 확인용 집행일, 집행내역, 금액, 첨부자료 입력</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구현확인</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SettlementExecution 계열 route가 존재함</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스토리보드 Ver3.0 추가</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin.settlements.executions.store/download</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">운영 데이터 기준 저장/노출 최종 검수</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">채널 정산 화면에 집행현황이 같이 노출되어야 함</t>
         </is>
       </c>
     </row>
@@ -4443,22 +5374,72 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">자사PG/공용PG/포인트 정산 산식 확정표</t>
+          <t xml:space="preserve">RF-02-08-02-3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">이메일과 Ver3.0 정산 가이드의 금액 표기 기준을 코드/엑셀 컬럼에 고정해야 함</t>
+          <t xml:space="preserve">전체관리자</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-02-08 전체</t>
+          <t xml:space="preserve">정산 관리</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">자사PG 결제 금액을 매출/지급액에 중복 또는 반대로 반영할 위험</t>
+          <t xml:space="preserve">자사PG 채널 지급액 상세 표기</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요구사항</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자사PG 12,500원 결제 시 Me9가 지급할 채널 지급액은 0으로 표기. 포인트 결제가 있으면 포인트 예수금 기준 금액만 별도 반영</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반영기준</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스토리보드 Ver3.0 가이드상 자사PG 결제액은 Me9 정산 지급 대상이 아님</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정산 메일 2번 / 11111.png / 22222.png</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin.settlements.payout</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자사PG/공용PG/자사포인트/Me9포인트/상품가/배송비/정산비용 컬럼 분리 유지</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">많은 건수에서 혼동 방지를 위해 PG구분/상품유형/구분 필터 또는 상세 링크 필요</t>
         </is>
       </c>
     </row>
@@ -4470,22 +5451,72 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shop 전용 로그인/간편가입 사용 여부 결정</t>
+          <t xml:space="preserve">RF-02-08-02-4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">현재는 공통 회원 화면 재사용 가능성이 있으나 스토리보드는 Shop 전용 화면을 제시함</t>
+          <t xml:space="preserve">전체관리자</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RF-03-01-02, RF-03-02-01</t>
+          <t xml:space="preserve">정산 관리</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">별도 화면을 만들어야 하는지 공통 라우트 연결이면 되는지 불명확</t>
+          <t xml:space="preserve">채널 청구액 상세 표기</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요구사항</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMS 수수료, 지급포인트, 매입/수수료를 채널 청구액 상세로 분리</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반영기준</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">청구액은 지급액과 다른 상세 목록으로 확인되어야 함</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스토리보드 Ver3.0 추가</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin.settlements.billing</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상세/엑셀 컬럼 및 합계 검증</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자사PG 이용 시 지급포인트 제공 불가 조건 포함</t>
         </is>
       </c>
     </row>
@@ -4497,6 +5528,310 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t xml:space="preserve">RF-02-08-01-3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">채널 관리자</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정산 관리</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정산 엑셀 상세</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요구사항</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">등록일, 주문번호, 주문유형, 상품유형, 구분, PG결제, 포인트결제, 상품가, 배송비, 할인금액, 수수료, SMS, 제공포인트, 정산비용 표시</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확인필요</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 export는 있으나 스토리보드 컬럼과 완전 동일 여부 확인 필요</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스토리보드 Ver3.0 추가</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin.settlements.export</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">엑셀 컬럼 순서/명칭/산식 대조</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">출력 파일 확장자가 CSV면 실제 xlsx 요구 여부 결정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-02-08-01-4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">채널 관리자</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정산 관리</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추가 배송비 엑셀 상세</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요구사항</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">완료일시, 반품/교환 주문번호, 원주문번호, 주문상태, 주문유형, 상품유형, 결제비용, 추가배송비 표시</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-28</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확인필요</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 extra shipping export는 있으나 컬럼 완전 일치 확인 필요</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스토리보드 Ver3.0 추가</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin.settlements.extra_shipping.export</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추가배송비 상세 산출 기준 검증</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반품/교환 배송비는 일반 정산과 분리 출력</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필요 문서/결정</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필요 이유</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대상 화면 ID</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">없을 경우 위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shop 채널 최신 퍼블리싱 원본 또는 캡처 묶음</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FileMap RF-03 대부분이 Shop 채널 별도 화면을 전제로 함</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-03 전체</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공통 회원/주문 화면 재사용 여부를 임의 판단하게 되어 의도와 다른 화면이 될 수 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">취소/반품/교환 상태 전이표</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용자 신청, 채널관리자 승인/보류/송장/옵션 변경, 발주사 흐름이 연결됨</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-01-06, RF-01-07-18, RF-02-07, RF-03-05</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태값은 저장되지만 실제 운영 흐름이 끊길 수 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자사PG/공용PG/포인트 정산 산식 확정표</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이메일과 Ver3.0 정산 가이드의 금액 표기 기준을 코드/엑셀 컬럼에 고정해야 함</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-02-08 전체</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자사PG 결제 금액을 매출/지급액에 중복 또는 반대로 반영할 위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shop 전용 로그인/간편가입 사용 여부 결정</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재는 공통 회원 화면 재사용 가능성이 있으나 스토리보드는 Shop 전용 화면을 제시함</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-03-01-02, RF-03-02-01</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">별도 화면을 만들어야 하는지 공통 라우트 연결이면 되는지 불명확</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t xml:space="preserve">팝업/레이어를 반드시 별도 파일로 요구하는지 여부</t>
         </is>
       </c>
@@ -4513,6 +5848,60 @@
       <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve">기능은 동작하나 검수에서 화면 형태 불일치로 재작업될 수 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">메인/대시보드 실제 데이터 항목 정의서</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인덱스 화면은 단순 페이지가 아니라 어떤 데이터를 어떤 기간/조건으로 집계할지 정의가 필요</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-01-01, RF-02-02-01, RF-05-02-01</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정적 숫자/샘플 차트가 남아도 구현 완료로 오판될 수 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">운영 미사용 샘플 파일 정리 기준</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop/sub, master/sub, admin/sub, front/cart index 계열이 실제 운영 화면인지 퍼블리싱 참고인지 결정 필요</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-03, RF-05</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중복 파일 때문에 링크 연결/검수 기준이 흔들릴 수 있음</t>
         </is>
       </c>
     </row>
